--- a/artfynd/A 55860-2022 artfynd.xlsx
+++ b/artfynd/A 55860-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55860-2022 artfynd.xlsx
+++ b/artfynd/A 55860-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100976757</v>
+        <v>100419967</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>690</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,17 +718,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vallebo O om 3, Sm</t>
+          <t>Vallebo O om 1, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480713.7414278775</v>
+        <v>480780</v>
       </c>
       <c r="R2" t="n">
-        <v>6394629.575916427</v>
+        <v>6394685</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,32 +752,22 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>F-Näs-0677</t>
+          <t>F-Näs-0676</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kan mycket väl finnas fler plantor i närheten de är inte alldeles enkla att finna, de gömmer sig nere i mossan.</t>
+          <t>Knäroten är funnen inom denna polygon, kanske gömmer den sig på andra ställen i närområdet eller på andra ställen i skogen, inte alldeles enkel att finna när den inte blommar. Det fanns fröställningar här från förra årets blomning.  Ytan utökad något den 19 maj då jag fann 5-tal ex lite längre in åt SV, plantorna är inte alltid lätta att upptäcka de gömmer sig i mossan</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,6 +779,11 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Mossrik barrskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -814,15 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100590499</v>
+        <v>100419995</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -847,24 +832,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vallebo O om, Sm</t>
+          <t>Vallebo O om 2, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480649.5412537943</v>
+        <v>480639</v>
       </c>
       <c r="R3" t="n">
-        <v>6394642.710721541</v>
+        <v>6394635</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,29 +879,24 @@
           <t>Nässjö</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>F-Näs-0675</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Punkterna är ett urval av alla koordinater inom polygonen som tillhör floraväkteriet. Antal skott är sammanräknade inom floraväkteriets data.</t>
+          <t>Knäroten är funnen inom denna polygon, kanske gömmer den sig på andra ställen i närområdet eller på andra ställen i skogen, inte alldeles enkel att finna när den inte blommar. Det fanns fröställningar här från förra årets blomning. Växer mellan tre olika hjulspår/"vägar" som skogsmaskiner skapat. Ytan utökad något den 19 maj då jag fann 35-tal ex lite längre in, plantorna är inte alltid lätta att upptäcka de gömmer sig i mossan</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,19 +925,18 @@
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>100590498</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480634.5597354988</v>
+        <v>480635</v>
       </c>
       <c r="R4" t="n">
-        <v>6394645.454961035</v>
+        <v>6394645</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,19 +1005,9 @@
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-04-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1068,15 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100590510</v>
+        <v>100590499</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480767.0650488664</v>
+        <v>480650</v>
       </c>
       <c r="R5" t="n">
-        <v>6394693.995348161</v>
+        <v>6394643</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1145,19 +1117,9 @@
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-04-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1195,15 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100590508</v>
+        <v>100590500</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480781.5668899021</v>
+        <v>480633</v>
       </c>
       <c r="R6" t="n">
-        <v>6394703.012640005</v>
+        <v>6394644</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1272,19 +1229,9 @@
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-04-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1322,15 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100590506</v>
+        <v>100590502</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480802.3017214888</v>
+        <v>480636</v>
       </c>
       <c r="R7" t="n">
-        <v>6394671.379237696</v>
+        <v>6394634</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1399,19 +1341,9 @@
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-04-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1449,15 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100590502</v>
+        <v>100590503</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1493,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480635.5744123077</v>
+        <v>480632</v>
       </c>
       <c r="R8" t="n">
-        <v>6394633.691199903</v>
+        <v>6394657</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1526,19 +1453,9 @@
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-04-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1576,15 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100590500</v>
+        <v>100590504</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480633.4835901138</v>
+        <v>480624</v>
       </c>
       <c r="R9" t="n">
-        <v>6394644.391128807</v>
+        <v>6394656</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1653,19 +1565,9 @@
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-04-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1703,15 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>100590503</v>
+        <v>100590505</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480632.4714838699</v>
+        <v>480785</v>
       </c>
       <c r="R10" t="n">
-        <v>6394656.689340405</v>
+        <v>6394683</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1780,19 +1677,9 @@
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-04-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1830,15 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100419995</v>
+        <v>100590506</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1863,32 +1745,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vallebo O om 2, Sm</t>
+          <t>Vallebo O om, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480638.7926106165</v>
+        <v>480802</v>
       </c>
       <c r="R11" t="n">
-        <v>6394634.744772248</v>
+        <v>6394671</v>
       </c>
       <c r="S11" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1910,34 +1784,19 @@
           <t>Nässjö</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>F-Näs-0675</t>
-        </is>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Knäroten är funnen inom denna polygon, kanske gömmer den sig på andra ställen i närområdet eller på andra ställen i skogen, inte alldeles enkel att finna när den inte blommar. Det fanns fröställningar här från förra årets blomning. Växer mellan tre olika hjulspår/"vägar" som skogsmaskiner skapat. Ytan utökad något den 19 maj då jag fann 35-tal ex lite längre in, plantorna är inte alltid lätta att upptäcka de gömmer sig i mossan</t>
+          <t>Punkterna är ett urval av alla koordinater inom polygonen som tillhör floraväkteriet. Antal skott är sammanräknade inom floraväkteriets data.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1966,23 +1825,14 @@
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100419967</v>
+        <v>100590507</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2007,32 +1857,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vallebo O om 1, Sm</t>
+          <t>Vallebo O om, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480779.8739479767</v>
+        <v>480785</v>
       </c>
       <c r="R12" t="n">
-        <v>6394684.848099071</v>
+        <v>6394682</v>
       </c>
       <c r="S12" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2054,34 +1896,19 @@
           <t>Nässjö</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>F-Näs-0676</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Knäroten är funnen inom denna polygon, kanske gömmer den sig på andra ställen i närområdet eller på andra ställen i skogen, inte alldeles enkel att finna när den inte blommar. Det fanns fröställningar här från förra årets blomning.  Ytan utökad något den 19 maj då jag fann 5-tal ex lite längre in åt SV, plantorna är inte alltid lätta att upptäcka de gömmer sig i mossan</t>
+          <t>Punkterna är ett urval av alla koordinater inom polygonen som tillhör floraväkteriet. Antal skott är sammanräknade inom floraväkteriets data.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2110,23 +1937,14 @@
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>100590507</v>
+        <v>100590508</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,10 +1980,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480785.2163009102</v>
+        <v>480782</v>
       </c>
       <c r="R13" t="n">
-        <v>6394682.150246196</v>
+        <v>6394703</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2195,19 +2013,9 @@
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-04-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2245,15 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>100976164</v>
+        <v>100590509</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2279,16 +2082,20 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Vallebo O om, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480658.5349517268</v>
+        <v>480774</v>
       </c>
       <c r="R14" t="n">
-        <v>6394619.684317742</v>
+        <v>6394689</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2315,22 +2122,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-30</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2344,6 +2141,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2367,15 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>100590505</v>
+        <v>100590510</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2411,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480785.2213836896</v>
+        <v>480767</v>
       </c>
       <c r="R15" t="n">
-        <v>6394683.219201012</v>
+        <v>6394694</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2444,19 +2237,9 @@
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-04-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2494,15 +2277,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>100590643</v>
+        <v>100590642</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2538,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480652.721057711</v>
+        <v>480617</v>
       </c>
       <c r="R16" t="n">
-        <v>6394635.747056112</v>
+        <v>6394640</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2571,19 +2349,9 @@
           <t>2022-04-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-04-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2621,15 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>100976162</v>
+        <v>100590643</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2655,16 +2418,20 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Vallebo O om, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480770.1737992553</v>
+        <v>480653</v>
       </c>
       <c r="R17" t="n">
-        <v>6394672.06648519</v>
+        <v>6394636</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2691,22 +2458,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2720,6 +2477,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2743,15 +2501,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>100590509</v>
+        <v>100976162</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2777,20 +2530,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Vallebo O om, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480774.0037251351</v>
+        <v>480770</v>
       </c>
       <c r="R18" t="n">
-        <v>6394689.151934995</v>
+        <v>6394672</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2817,22 +2566,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-04-30</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-04-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2846,7 +2585,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2867,6 +2605,225 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>100976163</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vallebo O om, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>480714</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6394630</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-05-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-05-19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Antal skott är noterade inom floraväkteriets data.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Mossrik barrskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>100976164</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vallebo O om, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>480659</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6394620</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-05-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-05-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Punkterna är ett urval av alla koordinater inom polygonen som tillhör floraväkteriet. Antal skott är sammanräknade inom floraväkteriets data.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Mossrik barrskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55860-2022 artfynd.xlsx
+++ b/artfynd/A 55860-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100419967</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -928,6 +938,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100419995</t>
         </is>
       </c>
     </row>
@@ -1042,6 +1057,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590498</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1154,6 +1174,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590499</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1266,6 +1291,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590500</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1378,6 +1408,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590502</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1490,6 +1525,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590503</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1602,6 +1642,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590504</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1714,6 +1759,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590505</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1826,6 +1876,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590506</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1938,6 +1993,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590507</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2050,6 +2110,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590508</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2162,6 +2227,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590509</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2274,6 +2344,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590510</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2386,6 +2461,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590642</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2498,6 +2578,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100590643</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2605,6 +2690,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100976162</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2717,6 +2807,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100976163</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2824,8 +2919,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100976164</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>